--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2298">
   <si>
     <t>en</t>
   </si>
@@ -5542,6 +5542,18 @@
     <t>슐커</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (영감을 받아)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>시프트 (바닐라)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6454,6 +6466,12 @@
     <t>울트라킬</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>우마무스메</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6746,6 +6764,12 @@
   </si>
   <si>
     <t>겨울</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>겨울 신상품</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -7233,7 +7257,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15197,20 +15221,20 @@
         <v>1905</v>
       </c>
       <c r="B995" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B996" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B997" t="s">
         <v>1909</v>
@@ -15429,20 +15453,20 @@
         <v>1962</v>
       </c>
       <c r="B1024" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1025" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1026" t="s">
         <v>1966</v>
@@ -15477,20 +15501,20 @@
         <v>1973</v>
       </c>
       <c r="B1030" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1031" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1032" t="s">
         <v>1977</v>
@@ -15565,20 +15589,20 @@
         <v>1994</v>
       </c>
       <c r="B1041" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1042" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B1043" t="s">
         <v>1998</v>
@@ -15933,20 +15957,20 @@
         <v>2085</v>
       </c>
       <c r="B1087" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1088" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1089" t="s">
         <v>2089</v>
@@ -16149,20 +16173,20 @@
         <v>2138</v>
       </c>
       <c r="B1114" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1115" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1116" t="s">
         <v>2142</v>
@@ -16221,28 +16245,28 @@
         <v>2155</v>
       </c>
       <c r="B1123" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B1124" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="B1125" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="B1126" t="s">
         <v>2161</v>
@@ -16445,28 +16469,28 @@
         <v>2210</v>
       </c>
       <c r="B1151" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B1152" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B1153" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1154" t="s">
         <v>2216</v>
@@ -16581,100 +16605,100 @@
         <v>2243</v>
       </c>
       <c r="B1168" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="B1169" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="B1170" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="B1171" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="B1172" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="B1173" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="B1174" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="B1175" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="B1176" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="B1177" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="B1178" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="B1179" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B1180" t="s">
         <v>2264</v>
@@ -16693,52 +16717,52 @@
         <v>2267</v>
       </c>
       <c r="B1182" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="B1183" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="B1184" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="B1185" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="B1186" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="B1187" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="B1188" t="s">
         <v>2278</v>
@@ -16781,19 +16805,51 @@
         <v>2287</v>
       </c>
       <c r="B1193" t="s">
-        <v>2144</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B1194" t="s">
-        <v>2289</v>
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2297</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
